--- a/data/trans_orig/IP19D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19D-Estudios-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36952</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32308</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>52696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66262</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35499</t>
+          <t>35533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132288</t>
+          <t>131543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154329</t>
+          <t>155827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137184</t>
+          <t>136279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160631</t>
+          <t>161054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276308</t>
+          <t>275683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308787</t>
+          <t>309284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61813</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83898</t>
+          <t>83803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>74963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98929</t>
+          <t>99661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142551</t>
+          <t>142167</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173841</t>
+          <t>175198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39399</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86502</t>
+          <t>86844</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104519</t>
+          <t>104987</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>30812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48292</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206710</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237423</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212105</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241785</t>
+          <t>241549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>427426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466782</t>
+          <t>469310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>207297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247002</t>
+          <t>248226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27163</t>
+          <t>27260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31079</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44192</t>
+          <t>45376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60096</t>
+          <t>61095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91745</t>
+          <t>91838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>115330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>98671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123098</t>
+          <t>123536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196384</t>
+          <t>195814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231121</t>
+          <t>231400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97680</t>
+          <t>97138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122062</t>
+          <t>122177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102403</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128954</t>
+          <t>127006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209104</t>
+          <t>208399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>243889</t>
+          <t>243888</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57635</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86427</t>
+          <t>86410</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107644</t>
+          <t>108753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39439</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69272</t>
+          <t>67973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157786</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189593</t>
+          <t>187322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>156736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>190107</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323262</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367097</t>
+          <t>368551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183591</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>152466</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184650</t>
+          <t>185693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>315884</t>
+          <t>314041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>359062</t>
+          <t>357370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136598</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160507</t>
+          <t>160924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124589</t>
+          <t>124908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151751</t>
+          <t>150988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269647</t>
+          <t>267964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305520</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77942</t>
+          <t>78014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115071</t>
+          <t>114789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174340</t>
+          <t>175600</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>209575</t>
+          <t>209957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>61730</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53566</t>
+          <t>53249</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>89030</t>
+          <t>89009</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110865</t>
+          <t>111219</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>42658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65869</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195975</t>
+          <t>194832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225812</t>
+          <t>225331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>190170</t>
+          <t>190288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221690</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392829</t>
+          <t>395099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437516</t>
+          <t>437752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109721</t>
+          <t>111049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>159245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247456</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>288664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48453</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>199809</t>
+          <t>198162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220160</t>
+          <t>219597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>241982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271319</t>
+          <t>271159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>447859</t>
+          <t>449060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486133</t>
+          <t>485642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>40804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>49330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>78209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>94917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132237</t>
+          <t>131524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72066</t>
+          <t>70987</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85097</t>
+          <t>84377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98078</t>
+          <t>97380</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116693</t>
+          <t>115733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>174116</t>
+          <t>174211</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196971</t>
+          <t>196411</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34007</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>51315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,39 +9976,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>325569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>363788</t>
+          <t>363011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400066</t>
+          <t>401364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>675377</t>
+          <t>675793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>719595</t>
+          <t>719494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187968</t>
+          <t>186106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
